--- a/public/Excal-Student.xlsx
+++ b/public/Excal-Student.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer01\Thitipong\CKK_School\Front-AdminCKK\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AA424E-A870-4F61-9A7C-0916B4C17497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E1BCC9-94B9-4D78-9E03-122F85B71EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11190" yWindow="2790" windowWidth="14400" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex.Excal" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>นาย</t>
   </si>
@@ -62,13 +62,28 @@
   </si>
   <si>
     <t>ห้อง</t>
+  </si>
+  <si>
+    <t>ชื่อรูป</t>
+  </si>
+  <si>
+    <t>image001</t>
+  </si>
+  <si>
+    <t>image002</t>
+  </si>
+  <si>
+    <t>image003</t>
+  </si>
+  <si>
+    <t>เบอร์โทรผู้ปกครอง</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -78,6 +93,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -103,9 +125,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -324,10 +347,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -346,8 +369,14 @@
       <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1111</v>
       </c>
@@ -366,8 +395,14 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>1111111111</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2222</v>
       </c>
@@ -386,8 +421,14 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>2222222222</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3333</v>
       </c>
@@ -405,6 +446,12 @@
       </c>
       <c r="F4" s="1">
         <v>2</v>
+      </c>
+      <c r="G4">
+        <v>3333333333</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
